--- a/data/trans_camb/P16A11-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P16A11-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,36; 13,53</t>
+          <t>5,1; 13,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 9,22</t>
+          <t>1,08; 9,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,93; 15,87</t>
+          <t>5,82; 15,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,22; 12,74</t>
+          <t>5,02; 12,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 9,39</t>
+          <t>1,19; 9,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,45; 20,37</t>
+          <t>12,62; 19,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,64; 12,23</t>
+          <t>6,67; 12,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,32; 8,17</t>
+          <t>2,03; 8,29</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,61; 17,66</t>
+          <t>11,7; 17,58</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,65; 56,6</t>
+          <t>18,9; 55,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,94; 38,29</t>
+          <t>3,7; 39,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,8; 65,87</t>
+          <t>22,25; 64,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,69; 40,87</t>
+          <t>14,17; 40,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,41; 29,57</t>
+          <t>3,41; 28,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,37; 64,47</t>
+          <t>35,06; 63,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,15; 42,22</t>
+          <t>21,35; 42,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,45; 28,3</t>
+          <t>6,3; 28,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>36,94; 61,7</t>
+          <t>37,25; 61,07</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 4,74</t>
+          <t>1,26; 4,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,39; 5,96</t>
+          <t>2,57; 5,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,39; 9,71</t>
+          <t>2,87; 9,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 4,3</t>
+          <t>0,48; 4,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,6; 6,47</t>
+          <t>2,79; 6,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,08; 37,01</t>
+          <t>6,02; 37,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,81</t>
+          <t>1,34; 3,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,1; 5,89</t>
+          <t>3,02; 5,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,3; 25,13</t>
+          <t>6,41; 22,44</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,22; 84,35</t>
+          <t>16,31; 85,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,66; 107,61</t>
+          <t>35,33; 106,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52,3; 169,42</t>
+          <t>48,29; 164,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,5; 77,87</t>
+          <t>6,64; 79,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>37,04; 124,44</t>
+          <t>41,27; 135,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,52; 627,33</t>
+          <t>96,01; 735,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,36; 67,63</t>
+          <t>19,33; 69,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>43,15; 103,68</t>
+          <t>43,06; 98,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>97,38; 415,96</t>
+          <t>101,25; 377,26</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 5,49</t>
+          <t>-2,05; 5,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 5,13</t>
+          <t>-2,08; 5,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,68; 12,85</t>
+          <t>4,95; 12,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 4,27</t>
+          <t>-2,47; 4,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 2,78</t>
+          <t>-3,46; 2,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,61; 6,84</t>
+          <t>1,29; 6,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 3,6</t>
+          <t>-1,39; 4,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 2,92</t>
+          <t>-1,93; 2,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,02; 8,53</t>
+          <t>4,2; 8,61</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-21,58; 82,9</t>
+          <t>-23,14; 90,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-19,6; 82,03</t>
+          <t>-21,65; 84,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>57,6; 207,23</t>
+          <t>47,82; 199,32</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-37,34; 95,85</t>
+          <t>-36,71; 89,7</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-44,84; 69,03</t>
+          <t>-46,98; 61,19</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,42; 152,4</t>
+          <t>14,54; 155,51</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-16,06; 60,65</t>
+          <t>-17,68; 68,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-24,97; 51,01</t>
+          <t>-23,81; 50,81</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>47,94; 144,32</t>
+          <t>51,16; 156,58</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,2; 5,69</t>
+          <t>2,26; 5,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,6; 4,03</t>
+          <t>0,61; 3,96</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,0; 7,33</t>
+          <t>1,14; 7,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,43; 6,18</t>
+          <t>2,44; 6,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 2,96</t>
+          <t>-0,75; 3,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,8; 20,51</t>
+          <t>2,91; 22,76</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,88; 5,43</t>
+          <t>2,89; 5,39</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,87</t>
+          <t>0,38; 2,88</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,68; 14,85</t>
+          <t>3,71; 14,62</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>16,48; 47,53</t>
+          <t>17,1; 49,5</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,49; 33,99</t>
+          <t>4,52; 33,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,69; 60,53</t>
+          <t>8,93; 58,57</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13,53; 38,76</t>
+          <t>13,74; 40,04</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 18,88</t>
+          <t>-4,19; 20,1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,28; 126,74</t>
+          <t>16,69; 139,55</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,74; 38,73</t>
+          <t>18,88; 38,51</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,22; 20,51</t>
+          <t>2,51; 20,65</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>24,74; 106,28</t>
+          <t>24,97; 103,56</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A11-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P16A11-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11,2</t>
+          <t>9,81</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,4</t>
+          <t>15,38</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>14,56</t>
+          <t>13,29</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,1; 13,32</t>
+          <t>5,12; 13,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 9,23</t>
+          <t>1,1; 9,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,82; 15,32</t>
+          <t>5,6; 14,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,02; 12,76</t>
+          <t>5,35; 12,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 9,17</t>
+          <t>0,97; 9,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,62; 19,8</t>
+          <t>11,96; 19,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,67; 12,1</t>
+          <t>6,5; 11,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 8,29</t>
+          <t>2,19; 8,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,7; 17,58</t>
+          <t>10,39; 16,04</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>44,41%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,9; 55,5</t>
+          <t>19,13; 57,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,7; 39,58</t>
+          <t>3,49; 41,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22,25; 64,67</t>
+          <t>20,61; 62,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,17; 40,28</t>
+          <t>15,49; 40,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,41; 28,76</t>
+          <t>2,76; 29,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,06; 63,06</t>
+          <t>33,93; 61,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,35; 42,15</t>
+          <t>20,29; 41,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,3; 28,77</t>
+          <t>6,98; 28,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>37,25; 61,07</t>
+          <t>32,65; 55,78</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7,35</t>
+          <t>8,74</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,58</t>
+          <t>7,21</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>10,92</t>
+          <t>7,98</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 4,8</t>
+          <t>1,24; 4,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,57; 5,98</t>
+          <t>2,46; 6,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,87; 9,71</t>
+          <t>7,05; 10,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,11</t>
+          <t>0,43; 4,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,79; 6,77</t>
+          <t>2,8; 6,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,02; 37,0</t>
+          <t>5,43; 8,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,92</t>
+          <t>1,4; 4,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,02; 5,61</t>
+          <t>2,99; 5,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,41; 22,44</t>
+          <t>6,77; 9,3</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>114,86%</t>
+          <t>136,47%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>243,31%</t>
+          <t>120,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>176,03%</t>
+          <t>128,61%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,31; 85,58</t>
+          <t>17,74; 90,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>35,33; 106,3</t>
+          <t>33,18; 108,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48,29; 164,58</t>
+          <t>93,41; 193,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,64; 79,85</t>
+          <t>5,09; 78,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>41,27; 135,21</t>
+          <t>40,58; 129,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,01; 735,28</t>
+          <t>76,76; 169,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,33; 69,21</t>
+          <t>20,41; 75,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>43,06; 98,89</t>
+          <t>43,38; 101,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>101,25; 377,26</t>
+          <t>99,49; 170,75</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9,02</t>
+          <t>9,05</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,23</t>
+          <t>4,79</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6,52</t>
+          <t>6,8</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 5,66</t>
+          <t>-2,0; 5,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 5,27</t>
+          <t>-1,77; 5,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,95; 12,59</t>
+          <t>5,44; 12,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 4,08</t>
+          <t>-2,91; 3,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 2,63</t>
+          <t>-3,81; 2,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,29; 6,77</t>
+          <t>1,82; 7,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 4,02</t>
+          <t>-1,62; 3,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 2,91</t>
+          <t>-1,79; 2,88</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,2; 8,61</t>
+          <t>4,5; 8,93</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>115,08%</t>
+          <t>115,51%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>98,09%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-23,14; 90,54</t>
+          <t>-20,95; 90,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-21,65; 84,71</t>
+          <t>-19,04; 85,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>47,82; 199,32</t>
+          <t>56,26; 212,01</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-36,71; 89,7</t>
+          <t>-40,12; 88,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-46,98; 61,19</t>
+          <t>-50,89; 58,62</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14,54; 155,51</t>
+          <t>20,92; 173,91</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-17,68; 68,01</t>
+          <t>-21,64; 60,36</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-23,81; 50,81</t>
+          <t>-22,92; 47,51</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>51,16; 156,58</t>
+          <t>54,0; 154,08</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5,11</t>
+          <t>6,16</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,04</t>
+          <t>3,88</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6,64</t>
+          <t>5,01</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,26; 5,89</t>
+          <t>2,25; 5,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,96</t>
+          <t>0,47; 3,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,14; 7,09</t>
+          <t>4,62; 7,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,44; 6,34</t>
+          <t>2,27; 6,3</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 3,15</t>
+          <t>-0,69; 2,92</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,91; 22,76</t>
+          <t>2,14; 5,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,89; 5,39</t>
+          <t>2,82; 5,41</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,88</t>
+          <t>0,31; 2,86</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,71; 14,62</t>
+          <t>3,85; 6,42</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>34,14%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>17,1; 49,5</t>
+          <t>16,34; 47,26</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,52; 33,32</t>
+          <t>3,48; 32,41</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,93; 58,57</t>
+          <t>33,49; 65,11</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13,74; 40,04</t>
+          <t>12,77; 39,87</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 20,1</t>
+          <t>-3,93; 18,9</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,69; 139,55</t>
+          <t>11,92; 35,63</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,88; 38,51</t>
+          <t>18,11; 38,31</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,51; 20,65</t>
+          <t>1,99; 20,06</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>24,97; 103,56</t>
+          <t>24,95; 45,57</t>
         </is>
       </c>
     </row>
